--- a/output/pdf_financials_xlsx/VTX.xlsx
+++ b/output/pdf_financials_xlsx/VTX.xlsx
@@ -41281,10 +41281,10 @@
         </is>
       </c>
       <c r="F499" s="5" t="n">
-        <v>0.064369</v>
+        <v>-0.064369</v>
       </c>
       <c r="G499" s="5" t="n">
-        <v>0.110691</v>
+        <v>-0.110691</v>
       </c>
       <c r="H499" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/VTX.xlsx
+++ b/output/pdf_financials_xlsx/VTX.xlsx
@@ -932,10 +932,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001794</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001795</v>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
@@ -1706,10 +1706,10 @@
         <v>-0.064369</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.064369</v>
+        <v>-0.06257500000000001</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.064369</v>
+        <v>-0.062574</v>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
@@ -1806,10 +1806,10 @@
         <v>-0.064369</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.064369</v>
+        <v>-0.06257500000000001</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.064369</v>
+        <v>-0.062574</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -2022,10 +2022,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.160009</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.402583</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0.044</v>
@@ -2043,16 +2043,16 @@
         <v>0</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>2.591</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>11.628</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>11.628</v>
       </c>
     </row>
     <row r="35">
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.160009</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.402583</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0.044</v>
@@ -2123,16 +2123,16 @@
         <v>0</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>2.591</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>11.628</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>11.628</v>
       </c>
     </row>
     <row r="37">
@@ -2582,10 +2582,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.160009</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.405583</v>
+        <v>0.003</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>4.224</v>
@@ -2603,16 +2603,16 @@
         <v>4.008</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>6.308</v>
+        <v>3.717</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>5.352</v>
+        <v>4.322</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>16.309</v>
+        <v>4.681</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>16.309</v>
+        <v>4.681</v>
       </c>
     </row>
     <row r="49">
@@ -6919,7 +6919,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -10990,7 +10990,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -24886,7 +24886,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E265" s="5" t="n">
@@ -41199,7 +41199,7 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">

--- a/output/pdf_financials_xlsx/VTX.xlsx
+++ b/output/pdf_financials_xlsx/VTX.xlsx
@@ -1759,7 +1759,7 @@
         <v>0</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="E28" s="1" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>-0.06257500000000001</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.062574</v>
+        <v>0.501426</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -4775,13 +4775,13 @@
         <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>1.569</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>17.882</v>
+        <v>0.985</v>
       </c>
       <c r="G100" s="3" t="n">
         <v>22.846</v>
@@ -5255,31 +5255,31 @@
         <v>0</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>8.597</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>3.997</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>1.799</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>2.831</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>3.633</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>7.739</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>13.555</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>4.569</v>
       </c>
     </row>
     <row r="113">
@@ -26257,7 +26257,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E284" t="inlineStr">
         <is>
           <t>-</t>
@@ -26799,7 +26803,11 @@
           <t>Proceeds from disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E292" t="inlineStr">
         <is>
           <t>-</t>
@@ -26862,7 +26870,11 @@
           <t>Additions to intangible assets 8</t>
         </is>
       </c>
-      <c r="D293" t="inlineStr"/>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E293" t="inlineStr">
         <is>
           <t>-</t>
@@ -28342,7 +28354,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr"/>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E315" t="inlineStr">
         <is>
           <t>-</t>
@@ -29391,7 +29407,11 @@
           <t>Additions to intangible assets 11</t>
         </is>
       </c>
-      <c r="D330" t="inlineStr"/>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E330" t="inlineStr">
         <is>
           <t>-</t>
@@ -32402,7 +32422,11 @@
           <t>Additions to intangible assets 12</t>
         </is>
       </c>
-      <c r="D373" t="inlineStr"/>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E373" t="inlineStr">
         <is>
           <t>-</t>
@@ -32473,7 +32497,11 @@
           <t>Proceeds from disposal of property and equipment 10</t>
         </is>
       </c>
-      <c r="D374" t="inlineStr"/>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E374" t="inlineStr">
         <is>
           <t>-</t>
@@ -33936,7 +33964,11 @@
           <t>Amortization - intangible assets 11</t>
         </is>
       </c>
-      <c r="D395" t="inlineStr"/>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E395" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/VTX.xlsx
+++ b/output/pdf_financials_xlsx/VTX.xlsx
@@ -1514,10 +1514,8 @@
       <c r="E23" s="3" t="n">
         <v>-2.948</v>
       </c>
-      <c r="F23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F23" s="3" t="n">
+        <v>2.291</v>
       </c>
       <c r="G23" s="1" t="inlineStr">
         <is>
@@ -2157,7 +2155,7 @@
         <v>40.303</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0</v>
+        <v>30.198</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>55.197</v>
@@ -2268,31 +2266,31 @@
         <v>0</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>0.612</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>1.285</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.358</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>1.784</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>0.255</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>0.164</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>0.277</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>0.521</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
+        <v>0.959</v>
       </c>
     </row>
     <row r="41">
@@ -2308,31 +2306,31 @@
         <v>0</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>21.442</v>
+        <v>22.054</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>34.9</v>
+        <v>36.185</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>40.303</v>
+        <v>40.661</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0</v>
+        <v>31.982</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>55.197</v>
+        <v>55.452</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>71.366</v>
+        <v>71.53</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>60.842</v>
+        <v>61.119</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>44.473</v>
+        <v>44.994</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>44.473</v>
+        <v>45.432</v>
       </c>
     </row>
     <row r="42">
@@ -2588,31 +2586,31 @@
         <v>0.003</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>4.224</v>
+        <v>3.612</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>4.507</v>
+        <v>3.222</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>5.231</v>
+        <v>4.873</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>45.534</v>
+        <v>13.552</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>4.008</v>
+        <v>3.753</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>3.717</v>
+        <v>3.553</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>4.322</v>
+        <v>4.045</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>4.681</v>
+        <v>4.16</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>4.681</v>
+        <v>3.722</v>
       </c>
     </row>
     <row r="49">
@@ -3286,31 +3284,31 @@
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>4.967</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>11.896</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>12.134</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>20.371</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>29.76</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>27.556</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>21.112</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>27.207</v>
       </c>
     </row>
     <row r="65">
@@ -3406,31 +3404,31 @@
         <v>0</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>3.422</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>5.562</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>3.999</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>2.108</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>2.516</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>6.262</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>6.212</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>4.952</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>4.293</v>
       </c>
     </row>
     <row r="68">
@@ -4736,10 +4734,8 @@
       <c r="E99" s="3" t="n">
         <v>-2.948</v>
       </c>
-      <c r="F99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F99" s="3" t="n">
+        <v>2.291</v>
       </c>
       <c r="G99" s="1" t="inlineStr">
         <is>
@@ -5635,10 +5631,10 @@
         <v>0</v>
       </c>
       <c r="J121" s="3" t="n">
-        <v>0</v>
+        <v>-0.452</v>
       </c>
       <c r="K121" s="3" t="n">
-        <v>0</v>
+        <v>-0.98</v>
       </c>
       <c r="L121" s="3" t="n">
         <v>0</v>
@@ -8290,7 +8286,11 @@
           <t>Lease liabilities 12,23 17,242</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -12183,7 +12183,11 @@
           <t>Lease liabilities 12</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
@@ -15341,7 +15345,11 @@
           <t>Lease liabilities 25</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
@@ -15958,7 +15966,11 @@
           <t>Lease liabilities</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -17929,7 +17941,11 @@
           <t>Lease liabilities 11 19,130</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -27475,7 +27491,11 @@
           <t>Repurchase of common shares 15</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr"/>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E302" t="inlineStr">
         <is>
           <t>-</t>
@@ -30176,7 +30196,11 @@
           <t>Repurchase of common shares 17</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
           <t>-</t>
@@ -33828,7 +33852,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D393" t="inlineStr"/>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E393" t="inlineStr">
         <is>
           <t>-</t>
